--- a/docs/投资配置占比9月19号_四大类饼图.xlsx
+++ b/docs/投资配置占比9月19号_四大类饼图.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\123\IdeaProjects\build-web-site\personal-website\outputs\investment_mix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\123\PycharmProjects\langgraph-self-learn\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E1A10C-97CA-4853-8F1F-AD8451BFB8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5833F06-7082-45CF-81E2-95F771D1B4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="原始数据" sheetId="1" r:id="rId1"/>
     <sheet name="饼形图" sheetId="2" r:id="rId2"/>
+    <sheet name="后续操作计划" sheetId="3" r:id="rId3"/>
+    <sheet name="投资原则" sheetId="4" r:id="rId4"/>
+    <sheet name="情绪影响" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
   <si>
     <t>投资配置数据</t>
   </si>
@@ -206,6 +209,111 @@
   </si>
   <si>
     <t>锂矿扇区较小，标的名称用同色引线标注；所有比例按原始数值计算，未放大扇区。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="DengXian"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>海力士</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>买入</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>10月7号附近，海力士解禁</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>卖掉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>山金国际，降低有色持仓，</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>买入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>港股中芯国际</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="DengXian"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1手，卖掉科创50ETF</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>等于是释放5万的资金出来，总的现金大概是35左右了。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="DengXian"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>现金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>变化</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>9月21号，周一</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>短期很难上涨了，也已经买入了9万了，后续还有可调用港股资金5万，总共买入15万也可以了。不要满仓</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -215,7 +323,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0#"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -255,6 +363,24 @@
       <sz val="9"/>
       <name val="DengXian"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="DengXian"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="DengXian"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -379,7 +505,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -412,6 +538,24 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2981,4 +3125,87 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF42CCBB-64AF-4FF9-87AA-B6B06ACC3BC0}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="31.75" style="33" customWidth="1"/>
+    <col min="2" max="2" width="34.75" style="33" customWidth="1"/>
+    <col min="3" max="3" width="33.875" style="33" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="33"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="13.9">
+      <c r="A1" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="13.9">
+      <c r="A2" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="13.9">
+      <c r="A3" s="35"/>
+      <c r="B3" s="32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="32.25" customHeight="1">
+      <c r="A4" s="35"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="36" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="42.4">
+      <c r="A5" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A4"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F6E1EBD-EFA5-41D6-9BF6-80E6A55879E2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2E36CBF-A49D-42D6-870E-A946B85977E5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/投资配置占比9月19号_四大类饼图.xlsx
+++ b/docs/投资配置占比9月19号_四大类饼图.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\123\PycharmProjects\langgraph-self-learn\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5833F06-7082-45CF-81E2-95F771D1B4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E49E7DCC-51D7-4132-AE01-2AE27827DB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="原始数据" sheetId="1" r:id="rId1"/>
     <sheet name="饼形图" sheetId="2" r:id="rId2"/>
     <sheet name="后续操作计划" sheetId="3" r:id="rId3"/>
     <sheet name="投资原则" sheetId="4" r:id="rId4"/>
-    <sheet name="情绪影响" sheetId="5" r:id="rId5"/>
+    <sheet name="买卖原则" sheetId="6" r:id="rId5"/>
+    <sheet name="追踪标的" sheetId="7" r:id="rId6"/>
+    <sheet name="情绪影响" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="88">
   <si>
     <t>投资配置数据</t>
   </si>
@@ -315,6 +317,159 @@
     <t>短期很难上涨了，也已经买入了9万了，后续还有可调用港股资金5万，总共买入15万也可以了。不要满仓</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>放弃一把暴富的幻想，总用可以挣几倍来安稳自己眼前不断加重的损失，还有可以回本的机会，结果就是越亏越严重，把所有希望寄希望与一次小概率翻盘上，心理压力越来越大，动作越来越变形</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>科技为主线，锂矿股博取超额收益，拒绝变成彻彻底底的赌狗，单压一只，把自己搞死</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>买之前就知道大概可以涨到多少，有大概多少的收益，而不是想着两三个月内可以翻倍的可能性</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="DengXian"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>挣了钱，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>就要享受，让自己放松下来最重要，不要继续瞎折腾了，心理安稳，精神放松才行</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>远离还债模式，你会被消耗，透支的</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>买入原则</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>止损原则</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2跌破20日均线</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 放量大阴线</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>远期估值，高赔率</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="DengXian"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>近期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>涨幅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="DengXian"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>下跌买入</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>均线原则，20日均线，20周均线</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>分批买入原则（50），后手原则（30），极端突发原则（20）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>总体仓位，7成基本仓，3分机动仓位，绝不满仓，绝不梭哈</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>spacx</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>宁德时代</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>杜绝慌慌张张，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>急急忙忙，非买不可的强迫症，否则一定会出错，百分百出错</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>一定要高赔率，少搞几次，但每次都要非常赚才行。在质量不在数量，否则做的越多，错的可能性越多</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>高确定性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>标的，必须成本低，才能挣到时间复利的钱，否则你根本享受不到</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到让自己心安，可以彻底放松的事物，比如音乐，固定工资，不要那么应激了，总觉得必须用尽全力，没有任何负债了才能彻底享受。你还是太缺乏安全感，太极端了</t>
+  </si>
 </sst>
 </file>
 
@@ -323,7 +478,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0#"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -381,6 +536,24 @@
       <sz val="11"/>
       <name val="DengXian"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="DengXian"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="DengXian"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <name val="DengXian"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -505,7 +678,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -537,9 +710,6 @@
     <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -549,13 +719,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1746,15 +1929,15 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="38" customHeight="1">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1" t="str">
         <f t="shared" si="1"/>
@@ -1772,15 +1955,15 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="38" customHeight="1">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="str">
         <f t="shared" si="1"/>
@@ -1798,15 +1981,15 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="38" customHeight="1">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3132,52 +3315,52 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="31.75" style="33" customWidth="1"/>
-    <col min="2" max="2" width="34.75" style="33" customWidth="1"/>
-    <col min="3" max="3" width="33.875" style="33" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="33"/>
+    <col min="1" max="1" width="31.75" style="32" customWidth="1"/>
+    <col min="2" max="2" width="34.75" style="32" customWidth="1"/>
+    <col min="3" max="3" width="33.875" style="32" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="13.9">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="31" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="13.9">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="31" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="13.9">
-      <c r="A3" s="35"/>
-      <c r="B3" s="32" t="s">
+      <c r="A3" s="37"/>
+      <c r="B3" s="31" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="32.25" customHeight="1">
-      <c r="A4" s="35"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="A4" s="37"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="34" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="42.4">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="35" t="s">
         <v>67</v>
       </c>
     </row>
@@ -3192,19 +3375,153 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F6E1EBD-EFA5-41D6-9BF6-80E6A55879E2}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="97.4375" style="32" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="13.9">
+      <c r="A1" s="31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="13.9">
+      <c r="A2" s="31" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="27.75">
+      <c r="A3" s="35" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="27.75">
+      <c r="A4" s="31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="27.75">
+      <c r="A5" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="13.9">
+      <c r="A6" s="31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="13.9">
+      <c r="A7" s="31"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E67C3F-344F-44D5-8426-D4964AE3170A}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="85.0625" style="32" customWidth="1"/>
+    <col min="2" max="2" width="30.125" style="32" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="46.15" customHeight="1">
+      <c r="A1" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="20.25">
+      <c r="A2" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="20.25">
+      <c r="A3" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="20.25">
+      <c r="A4" s="39" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="20.25" customHeight="1">
+      <c r="A5" s="41" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.85" customHeight="1">
+      <c r="A6" s="39" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D360B7-215B-4182-B1AE-47046958131A}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="13.9">
+      <c r="A1" s="38" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="13.9">
+      <c r="A2" s="38" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2E36CBF-A49D-42D6-870E-A946B85977E5}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="92.125" style="32" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="39" customHeight="1">
+      <c r="A1" s="31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="27.75">
+      <c r="A2" s="31" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="27.75">
+      <c r="A3" s="31" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
